--- a/data/trans_dic/P40_R2-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P40_R2-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con estado de salud regular, malo o muy malo (tasa de respuesta: 99,57%)</t>
+          <t>Población cuya salud autopercibida en los últimos 12 meses es regular, mala o muy mala (tasa de respuesta: 99,57%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>30,55%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>26,91%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>14,6; 20,56</t>
+          <t>14,61; 20,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>15,71; 21,61</t>
+          <t>15,5; 21,75</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14,46; 19,96</t>
+          <t>14,43; 20,25</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20,33; 26,74</t>
+          <t>19,89; 26,18</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>24,38; 31,54</t>
+          <t>24,63; 31,29</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,24; 30,95</t>
+          <t>24,46; 31,42</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,57; 32,61</t>
+          <t>25,85; 32,66</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>28,51; 33,84</t>
+          <t>27,96; 33,34</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>20,68; 25,11</t>
+          <t>20,64; 25,06</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20,95; 25,49</t>
+          <t>20,98; 25,45</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20,91; 25,53</t>
+          <t>20,9; 25,61</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>25,34; 29,6</t>
+          <t>24,9; 29,18</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>21,87%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>13,29; 17,71</t>
+          <t>13,19; 17,97</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14,15; 18,73</t>
+          <t>13,74; 18,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13,41; 17,89</t>
+          <t>13,43; 17,88</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,03; 17,4</t>
+          <t>13,92; 18,33</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>29,56; 35,63</t>
+          <t>29,44; 35,61</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,63; 29,48</t>
+          <t>23,78; 29,37</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,02; 27,81</t>
+          <t>21,6; 27,44</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>25,37; 30,12</t>
+          <t>25,25; 30,02</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>22,0; 25,83</t>
+          <t>22,16; 25,98</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19,58; 23,27</t>
+          <t>19,65; 23,45</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18,16; 21,86</t>
+          <t>18,19; 21,93</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>12,81; 22,68</t>
+          <t>20,27; 23,5</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>21,09%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12,45; 17,97</t>
+          <t>12,39; 18,16</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12,87; 18,95</t>
+          <t>13,08; 18,93</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13,1; 18,42</t>
+          <t>13,06; 18,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15,49; 21,81</t>
+          <t>14,89; 20,61</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>21,33; 27,98</t>
+          <t>21,52; 27,89</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23,58; 30,26</t>
+          <t>23,52; 30,33</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,17; 25,34</t>
+          <t>18,99; 25,43</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,9; 24,76</t>
+          <t>21,96; 27,25</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17,88; 22,05</t>
+          <t>17,79; 22,14</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>19,21; 23,6</t>
+          <t>19,18; 23,52</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>16,92; 20,89</t>
+          <t>16,91; 20,97</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12,73; 21,87</t>
+          <t>19,2; 22,93</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>23,7%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>13,83; 18,37</t>
+          <t>13,91; 18,34</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14,91; 20,11</t>
+          <t>14,96; 20,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13,62; 18,29</t>
+          <t>13,59; 18,22</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17,22; 22,2</t>
+          <t>16,78; 21,67</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>25,11; 31,01</t>
+          <t>25,14; 30,57</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,49; 30,26</t>
+          <t>24,32; 29,79</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,6; 28,49</t>
+          <t>22,84; 28,6</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>27,28; 46,49</t>
+          <t>25,58; 30,21</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>20,2; 23,95</t>
+          <t>20,2; 24,08</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20,64; 24,42</t>
+          <t>20,72; 24,61</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18,95; 22,8</t>
+          <t>19,04; 22,82</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>23,42; 35,61</t>
+          <t>21,98; 25,25</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>23,21%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>14,71; 17,33</t>
+          <t>14,75; 17,22</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15,61; 18,39</t>
+          <t>15,55; 18,41</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14,75; 17,31</t>
+          <t>14,71; 17,4</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14,06; 19,84</t>
+          <t>17,4; 20,02</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>26,93; 30,15</t>
+          <t>27,01; 30,19</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,36; 28,47</t>
+          <t>25,47; 28,49</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,67; 26,78</t>
+          <t>23,74; 26,8</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>22,89; 31,29</t>
+          <t>26,29; 28,81</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>21,4; 23,37</t>
+          <t>21,3; 23,41</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21,05; 23,04</t>
+          <t>20,89; 23,09</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19,77; 21,59</t>
+          <t>19,68; 21,74</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>19,98; 25,17</t>
+          <t>22,35; 24,11</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con estado de salud regular, malo o muy malo (tasa de respuesta: 99,57%)</t>
+          <t>Población cuya salud autopercibida en los últimos 12 meses es regular, mala o muy mala (tasa de respuesta: 99,57%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>149267</t>
+          <t>159182</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>209209</t>
+          <t>223883</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>358476</t>
+          <t>383065</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>101298; 142682</t>
+          <t>101407; 141725</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>109618; 150783</t>
+          <t>108173; 151779</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>96817; 133618</t>
+          <t>96635; 135599</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>129158; 169942</t>
+          <t>137354; 180803</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>167793; 217073</t>
+          <t>169557; 215390</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>167983; 214471</t>
+          <t>169469; 217728</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>170984; 218042</t>
+          <t>172804; 218382</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>192559; 228563</t>
+          <t>204849; 244283</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>285901; 347048</t>
+          <t>285300; 346478</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>291364; 354452</t>
+          <t>291700; 353957</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>279789; 341587</t>
+          <t>279713; 342651</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>332104; 388042</t>
+          <t>354428; 415340</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>157408</t>
+          <t>168965</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>265441</t>
+          <t>294586</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>422849</t>
+          <t>463550</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>127650; 170133</t>
+          <t>126715; 172650</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>142296; 188295</t>
+          <t>138112; 188803</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>136576; 182216</t>
+          <t>136755; 182127</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>71931; 207537</t>
+          <t>146052; 192296</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>286296; 345046</t>
+          <t>285101; 344824</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>242913; 302975</t>
+          <t>244441; 301836</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>227679; 287530</t>
+          <t>223382; 283796</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>243060; 288553</t>
+          <t>270395; 321486</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>424450; 498403</t>
+          <t>427568; 501282</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>398188; 473200</t>
+          <t>399514; 476779</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>372684; 448599</t>
+          <t>373364; 450033</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>275581; 487803</t>
+          <t>429713; 498238</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>130334</t>
+          <t>141364</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>172391</t>
+          <t>199293</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>302726</t>
+          <t>340658</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>84380; 121727</t>
+          <t>83917; 123053</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>95817; 141158</t>
+          <t>97384; 140954</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>99333; 139724</t>
+          <t>99039; 142094</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>109182; 153688</t>
+          <t>119538; 165553</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>145515; 190852</t>
+          <t>146798; 190242</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>182062; 233668</t>
+          <t>181644; 234178</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>148940; 196889</t>
+          <t>147561; 197658</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>83080; 231083</t>
+          <t>178342; 221325</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>243114; 299778</t>
+          <t>241865; 301018</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>291411; 358046</t>
+          <t>290964; 356830</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>259740; 320810</t>
+          <t>259698; 322059</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>208444; 358313</t>
+          <t>310092; 370382</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>182255</t>
+          <t>189016</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>356600</t>
+          <t>310849</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>538855</t>
+          <t>499865</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>130179; 172953</t>
+          <t>130971; 172657</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>139311; 187870</t>
+          <t>139796; 187368</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>126238; 169468</t>
+          <t>125927; 168867</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>159603; 205751</t>
+          <t>166149; 214551</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>260786; 322059</t>
+          <t>261133; 317532</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>255279; 315355</t>
+          <t>253472; 310467</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>233789; 294671</t>
+          <t>236232; 295810</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>298658; 509074</t>
+          <t>286298; 338032</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>399900; 474187</t>
+          <t>399952; 476796</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>407979; 482664</t>
+          <t>409558; 486480</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>371586; 447162</t>
+          <t>373367; 447554</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>473442; 719951</t>
+          <t>463560; 532640</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>619265</t>
+          <t>658528</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1003641</t>
+          <t>1028610</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1622905</t>
+          <t>1687138</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>481701; 567352</t>
+          <t>483004; 563588</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>528047; 622007</t>
+          <t>526094; 622642</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>497444; 583985</t>
+          <t>496042; 586909</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>486494; 686297</t>
+          <t>614602; 707202</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>909699; 1018360</t>
+          <t>912314; 1019541</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>896634; 1006458</t>
+          <t>900356; 1007094</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>831911; 941096</t>
+          <t>834271; 941753</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>838084; 1145921</t>
+          <t>981802; 1075953</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1423286; 1554451</t>
+          <t>1416684; 1557011</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1455899; 1594040</t>
+          <t>1445032; 1597084</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1361681; 1486878</t>
+          <t>1355349; 1497447</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1422663; 1792229</t>
+          <t>1624541; 1752315</t>
         </is>
       </c>
     </row>
